--- a/SeleniumTests/TestDataFolder/UserProfileTestDataValid.xlsx
+++ b/SeleniumTests/TestDataFolder/UserProfileTestDataValid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA73833-97D2-48D5-81E3-279C5F138BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00AB42F2-B081-4B77-A48A-7226E033B1ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UserProfileStoreTestData" sheetId="1" r:id="rId1"/>
@@ -481,13 +481,13 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>18</v>
